--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{227ED3AC-FD98-4FE6-8E7E-E5ADD2E39E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4589F0BF-377F-42A1-8D0F-E6B3ED88DD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12683" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4500" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4502" uniqueCount="925">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2899,6 +2899,9 @@
   </si>
   <si>
     <t>elc_won_IND_067</t>
+  </si>
+  <si>
+    <t>geothermal</t>
   </si>
 </sst>
 </file>
@@ -11595,10 +11598,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
-  <dimension ref="A9:J23"/>
+  <dimension ref="A9:J24"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.265625" customWidth="1"/>
     <col min="3" max="3" width="8.46484375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.06640625" bestFit="1" customWidth="1"/>
@@ -11744,7 +11747,7 @@
         <v>12</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" ref="B21:B23" si="0">"uce_buildrate_"&amp;A21</f>
+        <f t="shared" ref="B21:B24" si="0">"uce_buildrate_"&amp;A21</f>
         <v>uce_buildrate_wind</v>
       </c>
       <c r="C21" t="str">
@@ -11778,7 +11781,7 @@
         <v>uce_buildrate_hydro</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" ref="C22:C23" si="1">A22</f>
+        <f t="shared" ref="C22:C24" si="1">A22</f>
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
@@ -11827,6 +11830,34 @@
       </c>
       <c r="H23">
         <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>924</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>uce_buildrate_geothermal</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="1"/>
+        <v>geothermal</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4589F0BF-377F-42A1-8D0F-E6B3ED88DD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8A1FAE-5DBB-4C7F-B7AA-9D175143C8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4502" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4514" uniqueCount="931">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2902,6 +2902,24 @@
   </si>
   <si>
     <t>geothermal</t>
+  </si>
+  <si>
+    <t>Coal Low</t>
+  </si>
+  <si>
+    <t>Coal High</t>
+  </si>
+  <si>
+    <t>Gas Low</t>
+  </si>
+  <si>
+    <t>Gas High</t>
+  </si>
+  <si>
+    <t>Bio Low</t>
+  </si>
+  <si>
+    <t>Bio High</t>
   </si>
 </sst>
 </file>
@@ -11598,7 +11616,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
-  <dimension ref="A9:J24"/>
+  <dimension ref="A9:P27"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.59765625" bestFit="1" customWidth="1"/>
@@ -11613,12 +11631,12 @@
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>115</v>
       </c>
@@ -11646,8 +11664,26 @@
       <c r="J10" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="K10" t="s">
+        <v>925</v>
+      </c>
+      <c r="L10" t="s">
+        <v>926</v>
+      </c>
+      <c r="M10" t="s">
+        <v>927</v>
+      </c>
+      <c r="N10" t="s">
+        <v>928</v>
+      </c>
+      <c r="O10" t="s">
+        <v>929</v>
+      </c>
+      <c r="P10" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>116</v>
       </c>
@@ -11675,18 +11711,40 @@
       <c r="J11">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="K11">
+        <v>21</v>
+      </c>
+      <c r="L11">
+        <f>K11*1.5</f>
+        <v>31.5</v>
+      </c>
+      <c r="M11">
+        <v>3.2</v>
+      </c>
+      <c r="N11">
+        <f>M11*1.5</f>
+        <v>4.8000000000000007</v>
+      </c>
+      <c r="O11">
+        <f>K11/2</f>
+        <v>10.5</v>
+      </c>
+      <c r="P11">
+        <f>L11/2</f>
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="8" t="s">
         <v>43</v>
       </c>
@@ -11706,13 +11764,16 @@
         <v>2025</v>
       </c>
       <c r="G19" s="8">
+        <v>2027</v>
+      </c>
+      <c r="H19" s="8">
         <v>2040</v>
       </c>
-      <c r="H19" s="8">
+      <c r="I19" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -11734,20 +11795,20 @@
         <f>C11</f>
         <v>80</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <f>D11</f>
         <v>150</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" ref="B21:B24" si="0">"uce_buildrate_"&amp;A21</f>
+        <f t="shared" ref="B21:B27" si="0">"uce_buildrate_"&amp;A21</f>
         <v>uce_buildrate_wind</v>
       </c>
       <c r="C21" t="str">
@@ -11764,15 +11825,15 @@
         <f>E11</f>
         <v>30</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <f>F11</f>
         <v>60</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -11781,7 +11842,7 @@
         <v>uce_buildrate_hydro</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" ref="C22:C24" si="1">A22</f>
+        <f t="shared" ref="C22:C27" si="1">A22</f>
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
@@ -11791,18 +11852,21 @@
         <v>1</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <f>G11</f>
         <v>3</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <f>H11</f>
         <v>6</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -11821,18 +11885,21 @@
         <v>1</v>
       </c>
       <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
         <f>I11</f>
         <v>3</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <f>J11</f>
         <v>6</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>924</v>
       </c>
@@ -11857,7 +11924,109 @@
         <v>0</v>
       </c>
       <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>uce_buildrate_coal</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="1"/>
+        <v>coal</v>
+      </c>
+      <c r="D25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <f>K11</f>
+        <v>21</v>
+      </c>
+      <c r="H25">
+        <f>L11</f>
+        <v>31.5</v>
+      </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>uce_buildrate_gas</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="1"/>
+        <v>gas</v>
+      </c>
+      <c r="D26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f>M11</f>
+        <v>3.2</v>
+      </c>
+      <c r="H26">
+        <f>N11</f>
+        <v>4.8000000000000007</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>uce_buildrate_bioenergy</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="1"/>
+        <v>bioenergy</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f>O11</f>
+        <v>10.5</v>
+      </c>
+      <c r="H27">
+        <f>P11</f>
+        <v>15.75</v>
+      </c>
+      <c r="I27">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8A1FAE-5DBB-4C7F-B7AA-9D175143C8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B977231-5413-41A7-AB0E-DFFA76CF23E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2926,9 +2926,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -3056,7 +3057,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3074,6 +3075,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -11739,12 +11741,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="8" t="s">
         <v>43</v>
       </c>
@@ -11770,10 +11772,13 @@
         <v>2040</v>
       </c>
       <c r="I19" s="8">
+        <v>2050</v>
+      </c>
+      <c r="J19" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -11799,11 +11804,15 @@
         <f>D11</f>
         <v>150</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="15">
+        <f>H20*1.25</f>
+        <v>187.5</v>
+      </c>
+      <c r="J20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -11829,11 +11838,15 @@
         <f>F11</f>
         <v>60</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="15">
+        <f t="shared" ref="I21:I27" si="1">H21*1.25</f>
+        <v>75</v>
+      </c>
+      <c r="J21">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -11842,7 +11855,7 @@
         <v>uce_buildrate_hydro</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" ref="C22:C27" si="1">A22</f>
+        <f t="shared" ref="C22:C27" si="2">A22</f>
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
@@ -11862,11 +11875,15 @@
         <f>H11</f>
         <v>6</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="15">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="J22">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -11875,7 +11892,7 @@
         <v>uce_buildrate_nuclear</v>
       </c>
       <c r="C23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
@@ -11895,11 +11912,15 @@
         <f>J11</f>
         <v>6</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="15">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="J23">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>924</v>
       </c>
@@ -11908,7 +11929,7 @@
         <v>uce_buildrate_geothermal</v>
       </c>
       <c r="C24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>geothermal</v>
       </c>
       <c r="D24" t="s">
@@ -11926,11 +11947,15 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -11939,7 +11964,7 @@
         <v>uce_buildrate_coal</v>
       </c>
       <c r="C25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>coal</v>
       </c>
       <c r="D25" t="s">
@@ -11959,11 +11984,15 @@
         <f>L11</f>
         <v>31.5</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="15">
+        <f t="shared" si="1"/>
+        <v>39.375</v>
+      </c>
+      <c r="J25">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -11972,7 +12001,7 @@
         <v>uce_buildrate_gas</v>
       </c>
       <c r="C26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>gas</v>
       </c>
       <c r="D26" t="s">
@@ -11992,11 +12021,15 @@
         <f>N11</f>
         <v>4.8000000000000007</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="15">
+        <f t="shared" si="1"/>
+        <v>6.0000000000000009</v>
+      </c>
+      <c r="J26">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -12005,7 +12038,7 @@
         <v>uce_buildrate_bioenergy</v>
       </c>
       <c r="C27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>bioenergy</v>
       </c>
       <c r="D27" t="s">
@@ -12025,7 +12058,11 @@
         <f>P11</f>
         <v>15.75</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="15">
+        <f t="shared" si="1"/>
+        <v>19.6875</v>
+      </c>
+      <c r="J27">
         <v>4</v>
       </c>
     </row>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B977231-5413-41A7-AB0E-DFFA76CF23E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F669E16-B30E-48F2-9410-DF2E53071851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2929,7 +2929,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -3075,7 +3075,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -11728,12 +11728,12 @@
         <v>4.8000000000000007</v>
       </c>
       <c r="O11">
-        <f>K11/2</f>
-        <v>10.5</v>
+        <f>M11</f>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <f>L11/2</f>
-        <v>15.75</v>
+        <f>N11</f>
+        <v>4.8000000000000007</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.45">
@@ -12052,15 +12052,15 @@
       </c>
       <c r="G27">
         <f>O11</f>
-        <v>10.5</v>
+        <v>3.2</v>
       </c>
       <c r="H27">
         <f>P11</f>
-        <v>15.75</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="1"/>
-        <v>19.6875</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="J27">
         <v>4</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36461A77-6940-4016-BDB8-488351558458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26B0392-EFD1-4544-A4BC-34CEA8735A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4513" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4515" uniqueCount="932">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2917,6 +2917,12 @@
   </si>
   <si>
     <t>Bio High</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>-*gas*turbine*</t>
   </si>
 </sst>
 </file>
@@ -11736,12 +11742,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="8" t="s">
         <v>43</v>
       </c>
@@ -11772,8 +11778,11 @@
       <c r="J19" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K19" s="8" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -11807,7 +11816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -11841,7 +11850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -11878,7 +11887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -11915,7 +11924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>923</v>
       </c>
@@ -11950,7 +11959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -11987,7 +11996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -12023,8 +12032,11 @@
       <c r="J26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K26" s="1" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>50</v>
       </c>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26B0392-EFD1-4544-A4BC-34CEA8735A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E87EF67-ABC7-4954-B6AC-191B72B32B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4515" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4529" uniqueCount="938">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2923,6 +2923,24 @@
   </si>
   <si>
     <t>-*gas*turbine*</t>
+  </si>
+  <si>
+    <t>~tfm_ins</t>
+  </si>
+  <si>
+    <t>ncap_pkcnt</t>
+  </si>
+  <si>
+    <t>attrib_cond</t>
+  </si>
+  <si>
+    <t>e[_]*</t>
+  </si>
+  <si>
+    <t>-ncap_pkcnt</t>
+  </si>
+  <si>
+    <t>g[_]*</t>
   </si>
 </sst>
 </file>
@@ -11618,7 +11636,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
-  <dimension ref="A9:P27"/>
+  <dimension ref="A9:P34"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.59765625" bestFit="1" customWidth="1"/>
@@ -12073,6 +12091,66 @@
         <v>4</v>
       </c>
     </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>934</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>933</v>
+      </c>
+      <c r="C33" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,C22:C27)</f>
+        <v>hydro,nuclear,geothermal,coal,gas,bioenergy</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="E33" t="s">
+        <v>935</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>933</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="E34" t="s">
+        <v>935</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>937</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
